--- a/outputs/SAFIYA_прайс_по_брендам.xlsx
+++ b/outputs/SAFIYA_прайс_по_брендам.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИТОГО" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="РОСТ ЦЕН К 12.08" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЦЕНА ЗНАКОМОМУ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СКИДКА К ПУБЛИЧНОМУ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AESTURA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANUA" sheetId="5" state="visible" r:id="rId5"/>
@@ -508,12 +508,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было в прайсе 12.08, поз.</t>
+          <t>Есть в прайсе знакомому, поз.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1558,17 +1558,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3300,17 +3300,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3508,17 +3508,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -4478,17 +4478,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -4658,17 +4658,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -6050,17 +6050,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -6332,17 +6332,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Стало 01.09, $</t>
+          <t>Прайс 01.09, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
     </row>
@@ -13790,17 +13790,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -14276,17 +14276,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -14856,17 +14856,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -15452,17 +15452,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -15612,17 +15612,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -15806,17 +15806,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -16786,17 +16786,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -20202,17 +20202,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -20362,17 +20362,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -21564,17 +21564,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -21792,17 +21792,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -22020,17 +22020,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -22412,17 +22412,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Было 12.08, $</t>
+          <t>Знакомому 12.08, $</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Рост цены, %</t>
+          <t>Дороже, чем знакомому, %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Остаток был, шт</t>
+          <t>Остаток на 12.08, шт</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
